--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR221"/>
+  <dimension ref="A1:AR222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30608,7 +30608,7 @@
         <v>360.52</v>
       </c>
       <c r="J221" t="n">
-        <v>346.66</v>
+        <v>331.28</v>
       </c>
       <c r="K221" t="n">
         <v>356.3</v>
@@ -30671,7 +30671,7 @@
         <v>414.68</v>
       </c>
       <c r="AE221" t="n">
-        <v>416.21</v>
+        <v>414.89</v>
       </c>
       <c r="AF221" t="n">
         <v>413.4</v>
@@ -30710,6 +30710,144 @@
         <v>443.66</v>
       </c>
       <c r="AR221" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>375.57</v>
+      </c>
+      <c r="C222" t="n">
+        <v>350.97</v>
+      </c>
+      <c r="D222" t="n">
+        <v>344.59</v>
+      </c>
+      <c r="E222" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="F222" t="n">
+        <v>334.89</v>
+      </c>
+      <c r="G222" t="n">
+        <v>340.04</v>
+      </c>
+      <c r="H222" t="n">
+        <v>385.01</v>
+      </c>
+      <c r="I222" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="J222" t="n">
+        <v>311.89</v>
+      </c>
+      <c r="K222" t="n">
+        <v>357.34</v>
+      </c>
+      <c r="L222" t="n">
+        <v>397.48</v>
+      </c>
+      <c r="M222" t="n">
+        <v>435.59</v>
+      </c>
+      <c r="N222" t="n">
+        <v>448.39</v>
+      </c>
+      <c r="O222" t="n">
+        <v>440.83</v>
+      </c>
+      <c r="P222" t="n">
+        <v>428.28</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>418.44</v>
+      </c>
+      <c r="R222" t="n">
+        <v>408.93</v>
+      </c>
+      <c r="S222" t="n">
+        <v>398.99</v>
+      </c>
+      <c r="T222" t="n">
+        <v>394.85</v>
+      </c>
+      <c r="U222" t="n">
+        <v>391.37</v>
+      </c>
+      <c r="V222" t="n">
+        <v>388.64</v>
+      </c>
+      <c r="W222" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="X222" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>394.11</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>400.69</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>411.7</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>425.21</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>422.1</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>419.26</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>411.53</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>405.76</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>400.95</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>399.64</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>403.02</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>406.47</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>414.46</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>425.91</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>435.12</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>440.54</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>449.72</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>449.68</v>
+      </c>
+      <c r="AR222" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30726,7 +30864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32969,6 +33107,16 @@
       </c>
       <c r="B224" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -33137,28 +33285,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01497362074698534</v>
+        <v>0.01376223837070228</v>
       </c>
       <c r="J2" t="n">
+        <v>221</v>
+      </c>
+      <c r="K2" t="n">
         <v>220</v>
       </c>
-      <c r="K2" t="n">
-        <v>219</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001534384798419497</v>
+        <v>0.0001309218788853039</v>
       </c>
       <c r="M2" t="n">
-        <v>7.017671812032852</v>
+        <v>6.992193621767372</v>
       </c>
       <c r="N2" t="n">
-        <v>94.37922046723541</v>
+        <v>93.95961279432734</v>
       </c>
       <c r="O2" t="n">
-        <v>9.714896832557482</v>
+        <v>9.693276679963661</v>
       </c>
       <c r="P2" t="n">
-        <v>376.6108875064484</v>
+        <v>376.6225365309732</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33215,28 +33363,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3477059331796206</v>
+        <v>0.3387330479672701</v>
       </c>
       <c r="J3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04828221238275499</v>
+        <v>0.0462313427130836</v>
       </c>
       <c r="M3" t="n">
-        <v>9.457251372135058</v>
+        <v>9.453038673454312</v>
       </c>
       <c r="N3" t="n">
-        <v>154.6245933910103</v>
+        <v>154.4364685448574</v>
       </c>
       <c r="O3" t="n">
-        <v>12.43481376583543</v>
+        <v>12.42724702196176</v>
       </c>
       <c r="P3" t="n">
-        <v>352.3108204049788</v>
+        <v>352.396929757254</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33293,28 +33441,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009896643812288605</v>
+        <v>0.003520626634161732</v>
       </c>
       <c r="J4" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L4" t="n">
-        <v>5.026836888488706e-05</v>
+        <v>6.413264257432161e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>9.229728668999295</v>
+        <v>9.214844944489478</v>
       </c>
       <c r="N4" t="n">
-        <v>126.8676524069112</v>
+        <v>126.5471362779295</v>
       </c>
       <c r="O4" t="n">
-        <v>11.26355416406878</v>
+        <v>11.24931714718407</v>
       </c>
       <c r="P4" t="n">
-        <v>351.931374096586</v>
+        <v>351.9923776435759</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33371,28 +33519,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3914036927583726</v>
+        <v>-0.3970555669391922</v>
       </c>
       <c r="J5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05978066823896122</v>
+        <v>0.06192423569511496</v>
       </c>
       <c r="M5" t="n">
-        <v>10.48788904255292</v>
+        <v>10.46011289791956</v>
       </c>
       <c r="N5" t="n">
-        <v>156.0145532530195</v>
+        <v>155.5027647573033</v>
       </c>
       <c r="O5" t="n">
-        <v>12.49057857959428</v>
+        <v>12.47007476951535</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7196685538046</v>
+        <v>356.7739835113549</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33449,28 +33597,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6540984711621339</v>
+        <v>-0.6626030575684889</v>
       </c>
       <c r="J6" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K6" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1259563352725316</v>
+        <v>0.1297010496473272</v>
       </c>
       <c r="M6" t="n">
-        <v>11.52499056740261</v>
+        <v>11.50157799475388</v>
       </c>
       <c r="N6" t="n">
-        <v>191.3940239910445</v>
+        <v>190.9791907292606</v>
       </c>
       <c r="O6" t="n">
-        <v>13.83452290435216</v>
+        <v>13.81952208758539</v>
       </c>
       <c r="P6" t="n">
-        <v>362.6560895929334</v>
+        <v>362.7379870191889</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33527,28 +33675,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6125748214568986</v>
+        <v>-0.6195752266493121</v>
       </c>
       <c r="J7" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1023018997803784</v>
+        <v>0.105223279709169</v>
       </c>
       <c r="M7" t="n">
-        <v>12.12352195866669</v>
+        <v>12.09640396358352</v>
       </c>
       <c r="N7" t="n">
-        <v>212.2725728645727</v>
+        <v>211.6143620867622</v>
       </c>
       <c r="O7" t="n">
-        <v>14.56957696244379</v>
+        <v>14.54697089042121</v>
       </c>
       <c r="P7" t="n">
-        <v>364.8980900466657</v>
+        <v>364.9655025157279</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33605,28 +33753,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03021307446824983</v>
+        <v>0.02717374439789488</v>
       </c>
       <c r="J8" t="n">
+        <v>221</v>
+      </c>
+      <c r="K8" t="n">
         <v>220</v>
       </c>
-      <c r="K8" t="n">
-        <v>219</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001093991174308306</v>
+        <v>0.000893197197412543</v>
       </c>
       <c r="M8" t="n">
-        <v>5.465803848116241</v>
+        <v>5.456881529495104</v>
       </c>
       <c r="N8" t="n">
-        <v>53.92421674260643</v>
+        <v>53.73795307469704</v>
       </c>
       <c r="O8" t="n">
-        <v>7.343311020418952</v>
+        <v>7.330617509780267</v>
       </c>
       <c r="P8" t="n">
-        <v>387.8187192429155</v>
+        <v>387.8478463341885</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33687,28 +33835,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3286035648324015</v>
+        <v>-0.327024869491768</v>
       </c>
       <c r="J9" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K9" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1100279909096235</v>
+        <v>0.1100563252262671</v>
       </c>
       <c r="M9" t="n">
-        <v>5.358969720373913</v>
+        <v>5.342783463872094</v>
       </c>
       <c r="N9" t="n">
-        <v>56.70453290937822</v>
+        <v>56.46147653168499</v>
       </c>
       <c r="O9" t="n">
-        <v>7.530241225178528</v>
+        <v>7.514085209237715</v>
       </c>
       <c r="P9" t="n">
-        <v>363.9496425287188</v>
+        <v>363.934558595659</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33769,28 +33917,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3128420023782161</v>
+        <v>-0.3359253748184176</v>
       </c>
       <c r="J10" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03358047615284177</v>
+        <v>0.03918711913943729</v>
       </c>
       <c r="M10" t="n">
-        <v>10.44705657871112</v>
+        <v>10.38999195974773</v>
       </c>
       <c r="N10" t="n">
-        <v>182.0993935130764</v>
+        <v>179.8722201354773</v>
       </c>
       <c r="O10" t="n">
-        <v>13.49442082910847</v>
+        <v>13.41164494517646</v>
       </c>
       <c r="P10" t="n">
-        <v>332.7887454844284</v>
+        <v>333.0092107685629</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33851,28 +33999,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1661626868224519</v>
+        <v>-0.1503904475750753</v>
       </c>
       <c r="J11" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001844478726529597</v>
+        <v>0.001524104316220631</v>
       </c>
       <c r="M11" t="n">
-        <v>23.65528264613734</v>
+        <v>23.62726239604724</v>
       </c>
       <c r="N11" t="n">
-        <v>984.833579718515</v>
+        <v>981.802560548624</v>
       </c>
       <c r="O11" t="n">
-        <v>31.38205824541333</v>
+        <v>31.33372880058522</v>
       </c>
       <c r="P11" t="n">
-        <v>343.1110451223719</v>
+        <v>342.9596101654692</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33933,28 +34081,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8350010490880814</v>
+        <v>0.8370731576135838</v>
       </c>
       <c r="J12" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K12" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05606461394672735</v>
+        <v>0.05686474222598503</v>
       </c>
       <c r="M12" t="n">
-        <v>20.68829088805732</v>
+        <v>20.6035521773913</v>
       </c>
       <c r="N12" t="n">
-        <v>771.9967820017559</v>
+        <v>768.4506964856628</v>
       </c>
       <c r="O12" t="n">
-        <v>27.78483006969371</v>
+        <v>27.72094328275398</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4568687832936</v>
+        <v>372.4371382200894</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34015,28 +34163,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.533975834776636</v>
+        <v>1.53678649939297</v>
       </c>
       <c r="J13" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K13" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3094294942849</v>
+        <v>0.3123646390087714</v>
       </c>
       <c r="M13" t="n">
-        <v>13.89163936345362</v>
+        <v>13.84400149440153</v>
       </c>
       <c r="N13" t="n">
-        <v>345.2658605773706</v>
+        <v>343.7109768824098</v>
       </c>
       <c r="O13" t="n">
-        <v>18.5813309689422</v>
+        <v>18.53944381265009</v>
       </c>
       <c r="P13" t="n">
-        <v>390.8270495253126</v>
+        <v>390.8003186535257</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34097,28 +34245,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.647539086062999</v>
+        <v>1.647199577761312</v>
       </c>
       <c r="J14" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K14" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4170333654276198</v>
+        <v>0.4194006788545444</v>
       </c>
       <c r="M14" t="n">
-        <v>11.99416292212842</v>
+        <v>11.94104628897902</v>
       </c>
       <c r="N14" t="n">
-        <v>246.4671402750303</v>
+        <v>245.3424579347405</v>
       </c>
       <c r="O14" t="n">
-        <v>15.69927196640119</v>
+        <v>15.66341143987288</v>
       </c>
       <c r="P14" t="n">
-        <v>404.2980621339884</v>
+        <v>404.3013109792979</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34175,28 +34323,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.87934485622426</v>
+        <v>1.872741495752773</v>
       </c>
       <c r="J15" t="n">
+        <v>221</v>
+      </c>
+      <c r="K15" t="n">
         <v>220</v>
       </c>
-      <c r="K15" t="n">
-        <v>219</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5041665714159076</v>
+        <v>0.5046366850712916</v>
       </c>
       <c r="M15" t="n">
-        <v>11.40065974269756</v>
+        <v>11.38308354020444</v>
       </c>
       <c r="N15" t="n">
-        <v>224.7283752744294</v>
+        <v>223.9846583511084</v>
       </c>
       <c r="O15" t="n">
-        <v>14.99094310823803</v>
+        <v>14.96611700980279</v>
       </c>
       <c r="P15" t="n">
-        <v>397.9511781084083</v>
+        <v>398.0144606998708</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34253,28 +34401,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.835684729022596</v>
+        <v>1.819408344777323</v>
       </c>
       <c r="J16" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K16" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L16" t="n">
-        <v>0.511045756776199</v>
+        <v>0.5070768157468881</v>
       </c>
       <c r="M16" t="n">
-        <v>11.02755134708261</v>
+        <v>11.05655291392135</v>
       </c>
       <c r="N16" t="n">
-        <v>211.1450243401531</v>
+        <v>211.8883592605757</v>
       </c>
       <c r="O16" t="n">
-        <v>14.53083013252006</v>
+        <v>14.55638551497506</v>
       </c>
       <c r="P16" t="n">
-        <v>398.130683514203</v>
+        <v>398.2863234878394</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34331,28 +34479,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.661627728524536</v>
+        <v>1.642411412513633</v>
       </c>
       <c r="J17" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K17" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L17" t="n">
-        <v>0.38692699868281</v>
+        <v>0.3818218756154107</v>
       </c>
       <c r="M17" t="n">
-        <v>13.9997790811199</v>
+        <v>14.03103765384031</v>
       </c>
       <c r="N17" t="n">
-        <v>287.7859052851384</v>
+        <v>288.8593639099287</v>
       </c>
       <c r="O17" t="n">
-        <v>16.96425374972735</v>
+        <v>16.99586314106844</v>
       </c>
       <c r="P17" t="n">
-        <v>396.5065737817148</v>
+        <v>396.6899341878525</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34409,28 +34557,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.582592968326489</v>
+        <v>1.564384800024968</v>
       </c>
       <c r="J18" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K18" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3363136984253772</v>
+        <v>0.3319501283274535</v>
       </c>
       <c r="M18" t="n">
-        <v>14.40615567110096</v>
+        <v>14.42916400351981</v>
       </c>
       <c r="N18" t="n">
-        <v>321.1841296573115</v>
+        <v>321.8409928355342</v>
       </c>
       <c r="O18" t="n">
-        <v>17.92161068814161</v>
+        <v>17.93992733640619</v>
       </c>
       <c r="P18" t="n">
-        <v>387.9168443688189</v>
+        <v>388.0909801202491</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34487,28 +34635,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.198369368086939</v>
+        <v>1.180581536109463</v>
       </c>
       <c r="J19" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K19" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2387992895659353</v>
+        <v>0.2339886789623468</v>
       </c>
       <c r="M19" t="n">
-        <v>14.53150882509322</v>
+        <v>14.55047982626337</v>
       </c>
       <c r="N19" t="n">
-        <v>298.1500227374738</v>
+        <v>298.809317354588</v>
       </c>
       <c r="O19" t="n">
-        <v>17.2670212468009</v>
+        <v>17.28610185538047</v>
       </c>
       <c r="P19" t="n">
-        <v>387.766461987236</v>
+        <v>387.9372811517744</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34565,28 +34713,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8121680944300852</v>
+        <v>0.7983896555795386</v>
       </c>
       <c r="J20" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K20" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1165615607046537</v>
+        <v>0.1137282794112999</v>
       </c>
       <c r="M20" t="n">
-        <v>15.38802663125267</v>
+        <v>15.3740887073675</v>
       </c>
       <c r="N20" t="n">
-        <v>322.2862516040649</v>
+        <v>322.0196950235717</v>
       </c>
       <c r="O20" t="n">
-        <v>17.95233276218065</v>
+        <v>17.94490721691176</v>
       </c>
       <c r="P20" t="n">
-        <v>389.2819271172903</v>
+        <v>389.4146106630575</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34643,28 +34791,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2990921714247327</v>
+        <v>0.2913485182029145</v>
       </c>
       <c r="J21" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K21" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02046617229619163</v>
+        <v>0.01960948712134147</v>
       </c>
       <c r="M21" t="n">
-        <v>13.4630892589155</v>
+        <v>13.42662771757234</v>
       </c>
       <c r="N21" t="n">
-        <v>273.8589557465797</v>
+        <v>272.9844206922728</v>
       </c>
       <c r="O21" t="n">
-        <v>16.54868441135366</v>
+        <v>16.52224018383321</v>
       </c>
       <c r="P21" t="n">
-        <v>392.4363978068597</v>
+        <v>392.5113751359399</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34721,28 +34869,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0268447202390091</v>
+        <v>0.02233287353268908</v>
       </c>
       <c r="J22" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K22" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001928540216676877</v>
+        <v>0.0001347799725952559</v>
       </c>
       <c r="M22" t="n">
-        <v>12.25679663528176</v>
+        <v>12.2201758152239</v>
       </c>
       <c r="N22" t="n">
-        <v>238.967777715333</v>
+        <v>238.0042331735553</v>
       </c>
       <c r="O22" t="n">
-        <v>15.45858265544849</v>
+        <v>15.4273858178745</v>
       </c>
       <c r="P22" t="n">
-        <v>393.2461726479783</v>
+        <v>393.2898582580603</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34799,28 +34947,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1220939392348891</v>
+        <v>-0.1233626945273977</v>
       </c>
       <c r="J23" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K23" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005129122758040561</v>
+        <v>0.005288407878173085</v>
       </c>
       <c r="M23" t="n">
-        <v>10.82525905231281</v>
+        <v>10.78225973088403</v>
       </c>
       <c r="N23" t="n">
-        <v>186.4068156090927</v>
+        <v>185.5736039622199</v>
       </c>
       <c r="O23" t="n">
-        <v>13.65308813452446</v>
+        <v>13.6225402903504</v>
       </c>
       <c r="P23" t="n">
-        <v>393.5340332388104</v>
+        <v>393.5462284613495</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34877,28 +35025,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1969792913127624</v>
+        <v>-0.1941347069250758</v>
       </c>
       <c r="J24" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K24" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01400918338632462</v>
+        <v>0.01374555589506743</v>
       </c>
       <c r="M24" t="n">
-        <v>10.80975047882329</v>
+        <v>10.77723205940725</v>
       </c>
       <c r="N24" t="n">
-        <v>176.0561261479494</v>
+        <v>175.3110563940969</v>
       </c>
       <c r="O24" t="n">
-        <v>13.26861432659603</v>
+        <v>13.24050816223067</v>
       </c>
       <c r="P24" t="n">
-        <v>393.5015706694247</v>
+        <v>393.4742286438631</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34955,28 +35103,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09094541822202108</v>
+        <v>-0.08713169339452585</v>
       </c>
       <c r="J25" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K25" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003466385681592521</v>
+        <v>0.003212995924110174</v>
       </c>
       <c r="M25" t="n">
-        <v>10.19960290812118</v>
+        <v>10.17116189581363</v>
       </c>
       <c r="N25" t="n">
-        <v>153.2945342126251</v>
+        <v>152.6935789454358</v>
       </c>
       <c r="O25" t="n">
-        <v>12.38121699238912</v>
+        <v>12.35692433194587</v>
       </c>
       <c r="P25" t="n">
-        <v>392.0044353806148</v>
+        <v>391.9677780178838</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35033,28 +35181,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1022048577955626</v>
+        <v>-0.0952254782027904</v>
       </c>
       <c r="J26" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K26" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004358852205709085</v>
+        <v>0.003816701774025821</v>
       </c>
       <c r="M26" t="n">
-        <v>10.2201902694319</v>
+        <v>10.19743117129235</v>
       </c>
       <c r="N26" t="n">
-        <v>153.8238654029004</v>
+        <v>153.4382465503614</v>
       </c>
       <c r="O26" t="n">
-        <v>12.40257495050525</v>
+        <v>12.38701927625695</v>
       </c>
       <c r="P26" t="n">
-        <v>395.1040995594096</v>
+        <v>395.0370140561439</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35111,28 +35259,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2066827143274876</v>
+        <v>0.2178543545467931</v>
       </c>
       <c r="J27" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K27" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01759696753714901</v>
+        <v>0.01960666723574334</v>
       </c>
       <c r="M27" t="n">
-        <v>10.08575849277227</v>
+        <v>10.08742411685163</v>
       </c>
       <c r="N27" t="n">
-        <v>154.0591697841938</v>
+        <v>154.151021854631</v>
       </c>
       <c r="O27" t="n">
-        <v>12.4120574355823</v>
+        <v>12.41575699885557</v>
       </c>
       <c r="P27" t="n">
-        <v>392.8269211099523</v>
+        <v>392.7191527737737</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35189,28 +35337,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4412707517295714</v>
+        <v>0.4587389219400315</v>
       </c>
       <c r="J28" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K28" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L28" t="n">
-        <v>0.07247098735904889</v>
+        <v>0.07771923386575941</v>
       </c>
       <c r="M28" t="n">
-        <v>10.14373247985055</v>
+        <v>10.17235736926013</v>
       </c>
       <c r="N28" t="n">
-        <v>161.3087642263166</v>
+        <v>162.5256219842828</v>
       </c>
       <c r="O28" t="n">
-        <v>12.70073872758261</v>
+        <v>12.74855372127689</v>
       </c>
       <c r="P28" t="n">
-        <v>390.8089106252262</v>
+        <v>390.6403203955313</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35267,28 +35415,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6853425618472728</v>
+        <v>0.7069791000125895</v>
       </c>
       <c r="J29" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K29" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L29" t="n">
-        <v>0.15124884039411</v>
+        <v>0.1584001611310364</v>
       </c>
       <c r="M29" t="n">
-        <v>10.64286738588459</v>
+        <v>10.69390435885994</v>
       </c>
       <c r="N29" t="n">
-        <v>171.3625971970521</v>
+        <v>173.5932889995836</v>
       </c>
       <c r="O29" t="n">
-        <v>13.09055373913007</v>
+        <v>13.17548059842917</v>
       </c>
       <c r="P29" t="n">
-        <v>380.9502508985254</v>
+        <v>380.7418615333696</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35345,28 +35493,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7170388280698429</v>
+        <v>0.7423511125138686</v>
       </c>
       <c r="J30" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K30" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1544699277086897</v>
+        <v>0.1620834727964735</v>
       </c>
       <c r="M30" t="n">
-        <v>10.93638284770643</v>
+        <v>10.99955838323136</v>
       </c>
       <c r="N30" t="n">
-        <v>181.1596341106647</v>
+        <v>184.4083945055643</v>
       </c>
       <c r="O30" t="n">
-        <v>13.45955549454233</v>
+        <v>13.5797052436923</v>
       </c>
       <c r="P30" t="n">
-        <v>372.6380758382869</v>
+        <v>372.3936901358913</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35423,28 +35571,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6575771859750759</v>
+        <v>0.684762461053996</v>
       </c>
       <c r="J31" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K31" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1127051745116104</v>
+        <v>0.1198703643981371</v>
       </c>
       <c r="M31" t="n">
-        <v>11.97033085075254</v>
+        <v>12.05766413997289</v>
       </c>
       <c r="N31" t="n">
-        <v>217.3528722876224</v>
+        <v>221.0428320622218</v>
       </c>
       <c r="O31" t="n">
-        <v>14.74289226331192</v>
+        <v>14.86750927567297</v>
       </c>
       <c r="P31" t="n">
-        <v>368.0452614193824</v>
+        <v>367.7808179262174</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35501,28 +35649,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5405120742042876</v>
+        <v>0.5655471360850365</v>
       </c>
       <c r="J32" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K32" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06584373937026711</v>
+        <v>0.07132212805926375</v>
       </c>
       <c r="M32" t="n">
-        <v>12.41004415669298</v>
+        <v>12.46173412065805</v>
       </c>
       <c r="N32" t="n">
-        <v>264.6449781302233</v>
+        <v>267.3869136743419</v>
       </c>
       <c r="O32" t="n">
-        <v>16.26791253142896</v>
+        <v>16.3519697184878</v>
       </c>
       <c r="P32" t="n">
-        <v>367.2976173844934</v>
+        <v>367.0542329876667</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35579,28 +35727,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4381033681469493</v>
+        <v>0.4592711619651458</v>
       </c>
       <c r="J33" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K33" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L33" t="n">
-        <v>0.06785373893862789</v>
+        <v>0.07363475330847813</v>
       </c>
       <c r="M33" t="n">
-        <v>10.2397041363676</v>
+        <v>10.30719129177275</v>
       </c>
       <c r="N33" t="n">
-        <v>168.6847495776759</v>
+        <v>170.7097745187442</v>
       </c>
       <c r="O33" t="n">
-        <v>12.98786932401446</v>
+        <v>13.06559506944648</v>
       </c>
       <c r="P33" t="n">
-        <v>369.1648669910242</v>
+        <v>368.958662009851</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35657,28 +35805,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4198313154915324</v>
+        <v>0.4409549519305561</v>
       </c>
       <c r="J34" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K34" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L34" t="n">
-        <v>0.04281582410088969</v>
+        <v>0.04698060375058233</v>
       </c>
       <c r="M34" t="n">
-        <v>12.50889477073242</v>
+        <v>12.55260680651269</v>
       </c>
       <c r="N34" t="n">
-        <v>253.6943937892955</v>
+        <v>255.3611475153683</v>
       </c>
       <c r="O34" t="n">
-        <v>15.92778684529949</v>
+        <v>15.98002338907451</v>
       </c>
       <c r="P34" t="n">
-        <v>364.5926422897869</v>
+        <v>364.3886247614651</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -35735,28 +35883,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09215813854687852</v>
+        <v>0.1148800658841188</v>
       </c>
       <c r="J35" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K35" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L35" t="n">
-        <v>0.001976461671561514</v>
+        <v>0.003062690052340167</v>
       </c>
       <c r="M35" t="n">
-        <v>13.00503225903479</v>
+        <v>13.0657759034801</v>
       </c>
       <c r="N35" t="n">
-        <v>276.114862144826</v>
+        <v>278.1233043796506</v>
       </c>
       <c r="O35" t="n">
-        <v>16.6167043105673</v>
+        <v>16.67702924323306</v>
       </c>
       <c r="P35" t="n">
-        <v>370.2309053818267</v>
+        <v>370.0114511478253</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -35813,28 +35961,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3132404117322332</v>
+        <v>0.3348370625022432</v>
       </c>
       <c r="J36" t="n">
+        <v>221</v>
+      </c>
+      <c r="K36" t="n">
         <v>220</v>
       </c>
-      <c r="K36" t="n">
-        <v>219</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.02085353395521961</v>
+        <v>0.02376086238945707</v>
       </c>
       <c r="M36" t="n">
-        <v>13.01723015062972</v>
+        <v>13.0855035685957</v>
       </c>
       <c r="N36" t="n">
-        <v>295.2624834238729</v>
+        <v>296.8714765843846</v>
       </c>
       <c r="O36" t="n">
-        <v>17.18320352623087</v>
+        <v>17.22995869363547</v>
       </c>
       <c r="P36" t="n">
-        <v>368.8950288431378</v>
+        <v>368.6860972489689</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -35891,28 +36039,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3699459289473063</v>
+        <v>0.3872367814758471</v>
       </c>
       <c r="J37" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K37" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03828196025256325</v>
+        <v>0.04185968995583056</v>
       </c>
       <c r="M37" t="n">
-        <v>11.22189651468404</v>
+        <v>11.27484382485764</v>
       </c>
       <c r="N37" t="n">
-        <v>223.7225103198151</v>
+        <v>224.5903377810013</v>
       </c>
       <c r="O37" t="n">
-        <v>14.95735639475823</v>
+        <v>14.98633837136348</v>
       </c>
       <c r="P37" t="n">
-        <v>376.0505011919406</v>
+        <v>375.8849667363751</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -35969,28 +36117,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1303974647358767</v>
+        <v>0.1596329058260894</v>
       </c>
       <c r="J38" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K38" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L38" t="n">
-        <v>0.003122210207859299</v>
+        <v>0.004647298070744155</v>
       </c>
       <c r="M38" t="n">
-        <v>14.06001337005468</v>
+        <v>14.16487445786477</v>
       </c>
       <c r="N38" t="n">
-        <v>349.2682580650205</v>
+        <v>353.0752193343043</v>
       </c>
       <c r="O38" t="n">
-        <v>18.6887200756237</v>
+        <v>18.79029588203188</v>
       </c>
       <c r="P38" t="n">
-        <v>376.4029511172237</v>
+        <v>376.1199736973838</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -36047,28 +36195,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1487706107557658</v>
+        <v>0.1771461006943458</v>
       </c>
       <c r="J39" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K39" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L39" t="n">
-        <v>0.005830973760246883</v>
+        <v>0.008161347176887435</v>
       </c>
       <c r="M39" t="n">
-        <v>12.19114846668357</v>
+        <v>12.3081312851113</v>
       </c>
       <c r="N39" t="n">
-        <v>243.2595678615833</v>
+        <v>247.2122126358165</v>
       </c>
       <c r="O39" t="n">
-        <v>15.59678068902629</v>
+        <v>15.72298357932795</v>
       </c>
       <c r="P39" t="n">
-        <v>388.5812192854329</v>
+        <v>388.3067266105467</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -36125,28 +36273,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1139755282963341</v>
+        <v>0.1426162585871124</v>
       </c>
       <c r="J40" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K40" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L40" t="n">
-        <v>0.003356260633727404</v>
+        <v>0.005190015715272001</v>
       </c>
       <c r="M40" t="n">
-        <v>12.21545575849201</v>
+        <v>12.30441972248095</v>
       </c>
       <c r="N40" t="n">
-        <v>250.2829826052414</v>
+        <v>254.3378137442616</v>
       </c>
       <c r="O40" t="n">
-        <v>15.82033446565658</v>
+        <v>15.94797208877234</v>
       </c>
       <c r="P40" t="n">
-        <v>398.4115388052502</v>
+        <v>398.1349142379963</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -36203,28 +36351,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2187750235348583</v>
+        <v>0.2464481066166298</v>
       </c>
       <c r="J41" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K41" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L41" t="n">
-        <v>0.01135318945127983</v>
+        <v>0.01425316711909319</v>
       </c>
       <c r="M41" t="n">
-        <v>13.03873618013773</v>
+        <v>13.10300458423951</v>
       </c>
       <c r="N41" t="n">
-        <v>270.4223565809783</v>
+        <v>274.0352168499104</v>
       </c>
       <c r="O41" t="n">
-        <v>16.44452360456144</v>
+        <v>16.55400908692243</v>
       </c>
       <c r="P41" t="n">
-        <v>402.1448653010812</v>
+        <v>401.8775866893156</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -36281,28 +36429,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4002399976706835</v>
+        <v>0.4304181021034942</v>
       </c>
       <c r="J42" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L42" t="n">
-        <v>0.03428174712253029</v>
+        <v>0.03908950779031184</v>
       </c>
       <c r="M42" t="n">
-        <v>13.36290336768795</v>
+        <v>13.43973502574804</v>
       </c>
       <c r="N42" t="n">
-        <v>288.021827746686</v>
+        <v>292.2863413804392</v>
       </c>
       <c r="O42" t="n">
-        <v>16.97120584244638</v>
+        <v>17.09638386853896</v>
       </c>
       <c r="P42" t="n">
-        <v>404.2474417431487</v>
+        <v>403.9516185208744</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -36359,28 +36507,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4835859682554057</v>
+        <v>0.5097571856228673</v>
       </c>
       <c r="J43" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K43" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L43" t="n">
-        <v>0.04931670647579589</v>
+        <v>0.05425960792641737</v>
       </c>
       <c r="M43" t="n">
-        <v>13.3333720643036</v>
+        <v>13.41281212229227</v>
       </c>
       <c r="N43" t="n">
-        <v>294.0531803381017</v>
+        <v>297.0513566660785</v>
       </c>
       <c r="O43" t="n">
-        <v>17.14797889951179</v>
+        <v>17.23517788321544</v>
       </c>
       <c r="P43" t="n">
-        <v>405.903957626785</v>
+        <v>405.6520933441449</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -36418,7 +36566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR221"/>
+  <dimension ref="A1:AR222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84713,7 +84861,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>-34.46390321695263,172.6694717758247</t>
+          <t>-34.46400199011579,172.66958933764315</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -84818,7 +84966,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>-34.44961410838964,172.67602239538945</t>
+          <t>-34.44961638750531,172.6760364993388</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -84882,6 +85030,228 @@
         </is>
       </c>
       <c r="AR221" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>-34.46800276596885,172.66428244325368</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>-34.4676079224695,172.6650873763092</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>-34.4671017087787,172.6657464400734</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-34.46658803427512,172.6663957363369</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-34.46607175078382,172.66703869190835</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-34.46550489809376,172.6676090737044</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-34.46469819169822,172.66790080714364</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-34.4643577679302,172.6687542067252</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-34.46412651606872,172.66973755153978</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-34.46331398944603,172.67002905452372</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-34.462535562559395,172.670361149402</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-34.461816372666654,172.67065824132223</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-34.46128527707498,172.67093030010702</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-34.46069636985999,172.67126966251203</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-34.46003855407573,172.67170371073658</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>-34.459372381384746,172.67211002791578</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>-34.45870518562647,172.67251296704865</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>-34.45803930863939,172.67292030455866</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>-34.457355553823284,172.6732682951626</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>-34.456669759391225,172.67360953208754</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>-34.45598164806716,172.67394309461733</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>-34.455284872502226,172.67424790552792</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>-34.454579525272734,172.6745242724213</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>-34.45387518912694,172.67480401618562</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>-34.45315836831776,172.67504232275374</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>-34.45242789211748,172.6752353051868</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>-34.451722822327305,172.67540921439195</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>-34.451041158014554,172.6755882847386</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>-34.45033124875734,172.67578900697995</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>-34.449608842244956,172.67598980672153</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>-34.44889487236791,172.67624285423855</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>-34.448177511866334,172.6764749585045</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>-34.44745848738994,172.67669680458013</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>-34.44673341354957,172.67688125419733</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>-34.44600023587726,172.67701559390136</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>-34.4452669310701,172.6771491863201</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>-34.44452578153688,172.67723427318458</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>-34.4437786519672,172.67728239458182</t>
+        </is>
+      </c>
+      <c r="AN222" t="inlineStr">
+        <is>
+          <t>-34.44305216890694,172.67735081780467</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>-34.44233218073265,172.67741133223547</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>-34.441590260025116,172.67742484434558</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>-34.44085536465453,172.67753846267172</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR222"/>
+  <dimension ref="A1:AR224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30853,6 +30853,282 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>366</v>
+      </c>
+      <c r="C223" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="D223" t="n">
+        <v>335.86</v>
+      </c>
+      <c r="E223" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="F223" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="G223" t="n">
+        <v>330.51</v>
+      </c>
+      <c r="H223" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="I223" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="J223" t="n">
+        <v>295.84</v>
+      </c>
+      <c r="K223" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="L223" t="n">
+        <v>378.66</v>
+      </c>
+      <c r="M223" t="n">
+        <v>422.59</v>
+      </c>
+      <c r="N223" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="O223" t="n">
+        <v>431.49</v>
+      </c>
+      <c r="P223" t="n">
+        <v>418.96</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>408.88</v>
+      </c>
+      <c r="R223" t="n">
+        <v>400.38</v>
+      </c>
+      <c r="S223" t="n">
+        <v>394.56</v>
+      </c>
+      <c r="T223" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="U223" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="V223" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="W223" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="X223" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>387.96</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>392.82</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>400.24</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>410.94</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>409.11</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>403.55</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>393.88</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>386.44</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>388.02</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>396.8</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>411.55</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>418.24</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>425.04</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>432.07</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>427.89</v>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>365.38</v>
+      </c>
+      <c r="C224" t="n">
+        <v>341.41</v>
+      </c>
+      <c r="D224" t="n">
+        <v>336.09</v>
+      </c>
+      <c r="E224" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="F224" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="G224" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="H224" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="I224" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="J224" t="n">
+        <v>302.79</v>
+      </c>
+      <c r="K224" t="n">
+        <v>339.71</v>
+      </c>
+      <c r="L224" t="n">
+        <v>378.66</v>
+      </c>
+      <c r="M224" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="N224" t="n">
+        <v>442.68</v>
+      </c>
+      <c r="O224" t="n">
+        <v>436.27</v>
+      </c>
+      <c r="P224" t="n">
+        <v>424.74</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>414.36</v>
+      </c>
+      <c r="R224" t="n">
+        <v>402.69</v>
+      </c>
+      <c r="S224" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="T224" t="n">
+        <v>389.09</v>
+      </c>
+      <c r="U224" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="V224" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="W224" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="X224" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>389.38</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>394.55</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>400.12</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>408.16</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>406.95</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>399.78</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>377</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>402.99</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>410.07</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>416.27</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>424.2</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30864,7 +31140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B225"/>
+  <dimension ref="A1:B227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33117,6 +33393,26 @@
       </c>
       <c r="B225" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -33285,28 +33581,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01376223837070228</v>
+        <v>-0.004738223418922989</v>
       </c>
       <c r="J2" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K2" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001309218788853039</v>
+        <v>1.564444836710255e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>6.992193621767372</v>
+        <v>7.025803624921135</v>
       </c>
       <c r="N2" t="n">
-        <v>93.95961279432734</v>
+        <v>94.23283989948453</v>
       </c>
       <c r="O2" t="n">
-        <v>9.693276679963661</v>
+        <v>9.707360089101698</v>
       </c>
       <c r="P2" t="n">
-        <v>376.6225365309732</v>
+        <v>376.8010905926322</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33363,28 +33659,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3387330479672701</v>
+        <v>0.3061412447442645</v>
       </c>
       <c r="J3" t="n">
+        <v>223</v>
+      </c>
+      <c r="K3" t="n">
         <v>221</v>
       </c>
-      <c r="K3" t="n">
-        <v>219</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0462313427130836</v>
+        <v>0.03798673609378733</v>
       </c>
       <c r="M3" t="n">
-        <v>9.453038673454312</v>
+        <v>9.507587094632298</v>
       </c>
       <c r="N3" t="n">
-        <v>154.4364685448574</v>
+        <v>156.5307948697701</v>
       </c>
       <c r="O3" t="n">
-        <v>12.42724702196176</v>
+        <v>12.51122675319132</v>
       </c>
       <c r="P3" t="n">
-        <v>352.396929757254</v>
+        <v>352.7108410561006</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33441,28 +33737,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003520626634161732</v>
+        <v>-0.02288952075706194</v>
       </c>
       <c r="J4" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K4" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L4" t="n">
-        <v>6.413264257432161e-06</v>
+        <v>0.0002715113340783226</v>
       </c>
       <c r="M4" t="n">
-        <v>9.214844944489478</v>
+        <v>9.242942341292311</v>
       </c>
       <c r="N4" t="n">
-        <v>126.5471362779295</v>
+        <v>127.6893861524879</v>
       </c>
       <c r="O4" t="n">
-        <v>11.24931714718407</v>
+        <v>11.29997283857302</v>
       </c>
       <c r="P4" t="n">
-        <v>351.9923776435759</v>
+        <v>352.2459777843205</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33519,28 +33815,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3970555669391922</v>
+        <v>-0.4230583519863416</v>
       </c>
       <c r="J5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K5" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06192423569511496</v>
+        <v>0.07009040660440236</v>
       </c>
       <c r="M5" t="n">
-        <v>10.46011289791956</v>
+        <v>10.4578748970999</v>
       </c>
       <c r="N5" t="n">
-        <v>155.5027647573033</v>
+        <v>156.2971809276276</v>
       </c>
       <c r="O5" t="n">
-        <v>12.47007476951535</v>
+        <v>12.50188709466005</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7739835113549</v>
+        <v>357.024763884192</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33597,28 +33893,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6626030575684889</v>
+        <v>-0.6909189497862238</v>
       </c>
       <c r="J6" t="n">
+        <v>223</v>
+      </c>
+      <c r="K6" t="n">
         <v>221</v>
       </c>
-      <c r="K6" t="n">
-        <v>219</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1297010496473272</v>
+        <v>0.1402063847576018</v>
       </c>
       <c r="M6" t="n">
-        <v>11.50157799475388</v>
+        <v>11.49425476649317</v>
       </c>
       <c r="N6" t="n">
-        <v>190.9791907292606</v>
+        <v>191.8547512869923</v>
       </c>
       <c r="O6" t="n">
-        <v>13.81952208758539</v>
+        <v>13.85116425745476</v>
       </c>
       <c r="P6" t="n">
-        <v>362.7379870191889</v>
+        <v>363.0116295001886</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33675,28 +33971,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6195752266493121</v>
+        <v>-0.6475780911516784</v>
       </c>
       <c r="J7" t="n">
+        <v>223</v>
+      </c>
+      <c r="K7" t="n">
         <v>221</v>
       </c>
-      <c r="K7" t="n">
-        <v>219</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.105223279709169</v>
+        <v>0.1146437885123361</v>
       </c>
       <c r="M7" t="n">
-        <v>12.09640396358352</v>
+        <v>12.09894883523612</v>
       </c>
       <c r="N7" t="n">
-        <v>211.6143620867622</v>
+        <v>212.24806017935</v>
       </c>
       <c r="O7" t="n">
-        <v>14.54697089042121</v>
+        <v>14.56873570970899</v>
       </c>
       <c r="P7" t="n">
-        <v>364.9655025157279</v>
+        <v>365.2361152684759</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33753,28 +34049,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02717374439789488</v>
+        <v>0.01637079416873945</v>
       </c>
       <c r="J8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K8" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000893197197412543</v>
+        <v>0.0003283776592557519</v>
       </c>
       <c r="M8" t="n">
-        <v>5.456881529495104</v>
+        <v>5.464788839460554</v>
       </c>
       <c r="N8" t="n">
-        <v>53.73795307469704</v>
+        <v>53.66569174016204</v>
       </c>
       <c r="O8" t="n">
-        <v>7.330617509780267</v>
+        <v>7.325687117271801</v>
       </c>
       <c r="P8" t="n">
-        <v>387.8478463341885</v>
+        <v>387.9517008297405</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33835,28 +34131,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.327024869491768</v>
+        <v>-0.3434362720767928</v>
       </c>
       <c r="J9" t="n">
+        <v>223</v>
+      </c>
+      <c r="K9" t="n">
         <v>221</v>
       </c>
-      <c r="K9" t="n">
-        <v>219</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1100563252262671</v>
+        <v>0.1204546243987614</v>
       </c>
       <c r="M9" t="n">
-        <v>5.342783463872094</v>
+        <v>5.387273589118161</v>
       </c>
       <c r="N9" t="n">
-        <v>56.46147653168499</v>
+        <v>56.85150933387002</v>
       </c>
       <c r="O9" t="n">
-        <v>7.514085209237715</v>
+        <v>7.539993987654766</v>
       </c>
       <c r="P9" t="n">
-        <v>363.934558595659</v>
+        <v>364.091889254438</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33917,28 +34213,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3359253748184176</v>
+        <v>-0.376375011606028</v>
       </c>
       <c r="J10" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03918711913943729</v>
+        <v>0.04823519568147239</v>
       </c>
       <c r="M10" t="n">
-        <v>10.38999195974773</v>
+        <v>10.5274746391407</v>
       </c>
       <c r="N10" t="n">
-        <v>179.8722201354773</v>
+        <v>183.6898183305144</v>
       </c>
       <c r="O10" t="n">
-        <v>13.41164494517646</v>
+        <v>13.55322169561593</v>
       </c>
       <c r="P10" t="n">
-        <v>333.0092107685629</v>
+        <v>333.4000383594253</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33999,28 +34295,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1503904475750753</v>
+        <v>-0.1498663499317486</v>
       </c>
       <c r="J11" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K11" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001524104316220631</v>
+        <v>0.001543614398291093</v>
       </c>
       <c r="M11" t="n">
-        <v>23.62726239604724</v>
+        <v>23.41006009012935</v>
       </c>
       <c r="N11" t="n">
-        <v>981.802560548624</v>
+        <v>972.5871295010829</v>
       </c>
       <c r="O11" t="n">
-        <v>31.33372880058522</v>
+        <v>31.18632920850229</v>
       </c>
       <c r="P11" t="n">
-        <v>342.9596101654692</v>
+        <v>342.9545456167479</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -34081,28 +34377,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8370731576135838</v>
+        <v>0.810170479246432</v>
       </c>
       <c r="J12" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K12" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05686474222598503</v>
+        <v>0.05431273722892982</v>
       </c>
       <c r="M12" t="n">
-        <v>20.6035521773913</v>
+        <v>20.56652843353475</v>
       </c>
       <c r="N12" t="n">
-        <v>768.4506964856628</v>
+        <v>763.8103802836451</v>
       </c>
       <c r="O12" t="n">
-        <v>27.72094328275398</v>
+        <v>27.63711960902664</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4371382200894</v>
+        <v>372.694254129444</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34163,28 +34459,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.53678649939297</v>
+        <v>1.522901254972187</v>
       </c>
       <c r="J13" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K13" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3123646390087714</v>
+        <v>0.312359558314</v>
       </c>
       <c r="M13" t="n">
-        <v>13.84400149440153</v>
+        <v>13.78482264995272</v>
       </c>
       <c r="N13" t="n">
-        <v>343.7109768824098</v>
+        <v>341.1966113555847</v>
       </c>
       <c r="O13" t="n">
-        <v>18.53944381265009</v>
+        <v>18.47150809640579</v>
       </c>
       <c r="P13" t="n">
-        <v>390.8003186535257</v>
+        <v>390.9328280789409</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34245,28 +34541,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.647199577761312</v>
+        <v>1.634442445056105</v>
       </c>
       <c r="J14" t="n">
+        <v>223</v>
+      </c>
+      <c r="K14" t="n">
         <v>221</v>
       </c>
-      <c r="K14" t="n">
-        <v>219</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.4194006788545444</v>
+        <v>0.4199226288383859</v>
       </c>
       <c r="M14" t="n">
-        <v>11.94104628897902</v>
+        <v>11.8955204996125</v>
       </c>
       <c r="N14" t="n">
-        <v>245.3424579347405</v>
+        <v>243.6758903448462</v>
       </c>
       <c r="O14" t="n">
-        <v>15.66341143987288</v>
+        <v>15.61012140711424</v>
       </c>
       <c r="P14" t="n">
-        <v>404.3013109792979</v>
+        <v>404.4237917318454</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34323,28 +34619,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.872741495752773</v>
+        <v>1.848398033745952</v>
       </c>
       <c r="J15" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K15" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5046366850712916</v>
+        <v>0.5008746483874602</v>
       </c>
       <c r="M15" t="n">
-        <v>11.38308354020444</v>
+        <v>11.40957994975184</v>
       </c>
       <c r="N15" t="n">
-        <v>223.9846583511084</v>
+        <v>223.9468966557422</v>
       </c>
       <c r="O15" t="n">
-        <v>14.96611700980279</v>
+        <v>14.96485538372296</v>
       </c>
       <c r="P15" t="n">
-        <v>398.0144606998708</v>
+        <v>398.2485335289163</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34401,28 +34697,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.819408344777323</v>
+        <v>1.777289115220838</v>
       </c>
       <c r="J16" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K16" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5070768157468881</v>
+        <v>0.4933248533435786</v>
       </c>
       <c r="M16" t="n">
-        <v>11.05655291392135</v>
+        <v>11.16056366422459</v>
       </c>
       <c r="N16" t="n">
-        <v>211.8883592605757</v>
+        <v>215.9099960143179</v>
       </c>
       <c r="O16" t="n">
-        <v>14.55638551497506</v>
+        <v>14.69387613988623</v>
       </c>
       <c r="P16" t="n">
-        <v>398.2863234878394</v>
+        <v>398.6904961834879</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34479,28 +34775,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.642411412513633</v>
+        <v>1.594022468240795</v>
       </c>
       <c r="J17" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K17" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3818218756154107</v>
+        <v>0.3661002589984472</v>
       </c>
       <c r="M17" t="n">
-        <v>14.03103765384031</v>
+        <v>14.14159809303819</v>
       </c>
       <c r="N17" t="n">
-        <v>288.8593639099287</v>
+        <v>294.0827475642491</v>
       </c>
       <c r="O17" t="n">
-        <v>16.99586314106844</v>
+        <v>17.14884099769571</v>
       </c>
       <c r="P17" t="n">
-        <v>396.6899341878525</v>
+        <v>397.1533068761075</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34557,28 +34853,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.564384800024968</v>
+        <v>1.51699249916604</v>
       </c>
       <c r="J18" t="n">
+        <v>223</v>
+      </c>
+      <c r="K18" t="n">
         <v>221</v>
       </c>
-      <c r="K18" t="n">
-        <v>219</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3319501283274535</v>
+        <v>0.3178315156372211</v>
       </c>
       <c r="M18" t="n">
-        <v>14.42916400351981</v>
+        <v>14.54256204798929</v>
       </c>
       <c r="N18" t="n">
-        <v>321.8409928355342</v>
+        <v>326.2935704467642</v>
       </c>
       <c r="O18" t="n">
-        <v>17.93992733640619</v>
+        <v>18.06359793747536</v>
       </c>
       <c r="P18" t="n">
-        <v>388.0909801202491</v>
+        <v>388.5458335508163</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34635,28 +34931,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.180581536109463</v>
+        <v>1.140692108113617</v>
       </c>
       <c r="J19" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K19" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2339886789623468</v>
+        <v>0.2222918278333791</v>
       </c>
       <c r="M19" t="n">
-        <v>14.55047982626337</v>
+        <v>14.60774893435747</v>
       </c>
       <c r="N19" t="n">
-        <v>298.809317354588</v>
+        <v>301.3208763436908</v>
       </c>
       <c r="O19" t="n">
-        <v>17.28610185538047</v>
+        <v>17.35859661215995</v>
       </c>
       <c r="P19" t="n">
-        <v>387.9372811517744</v>
+        <v>388.3217236275236</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34713,28 +35009,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7983896555795386</v>
+        <v>0.762722814323612</v>
       </c>
       <c r="J20" t="n">
+        <v>223</v>
+      </c>
+      <c r="K20" t="n">
         <v>221</v>
       </c>
-      <c r="K20" t="n">
-        <v>219</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1137282794112999</v>
+        <v>0.1055081397265786</v>
       </c>
       <c r="M20" t="n">
-        <v>15.3740887073675</v>
+        <v>15.37826666890364</v>
       </c>
       <c r="N20" t="n">
-        <v>322.0196950235717</v>
+        <v>323.233099808639</v>
       </c>
       <c r="O20" t="n">
-        <v>17.94490721691176</v>
+        <v>17.97868459617218</v>
       </c>
       <c r="P20" t="n">
-        <v>389.4146106630575</v>
+        <v>389.7593153269318</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34791,28 +35087,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2913485182029145</v>
+        <v>0.2606711429292665</v>
       </c>
       <c r="J21" t="n">
+        <v>223</v>
+      </c>
+      <c r="K21" t="n">
         <v>221</v>
       </c>
-      <c r="K21" t="n">
-        <v>219</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.01960948712134147</v>
+        <v>0.01589924362239303</v>
       </c>
       <c r="M21" t="n">
-        <v>13.42662771757234</v>
+        <v>13.40652063971983</v>
       </c>
       <c r="N21" t="n">
-        <v>272.9844206922728</v>
+        <v>273.5301916004695</v>
       </c>
       <c r="O21" t="n">
-        <v>16.52224018383321</v>
+        <v>16.53874818722594</v>
       </c>
       <c r="P21" t="n">
-        <v>392.5113751359399</v>
+        <v>392.809459866609</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34869,28 +35165,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02233287353268908</v>
+        <v>-0.007018320609018787</v>
       </c>
       <c r="J22" t="n">
+        <v>223</v>
+      </c>
+      <c r="K22" t="n">
         <v>221</v>
       </c>
-      <c r="K22" t="n">
-        <v>219</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.0001347799725952559</v>
+        <v>1.342521879088565e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>12.2201758152239</v>
+        <v>12.23341653501891</v>
       </c>
       <c r="N22" t="n">
-        <v>238.0042331735553</v>
+        <v>238.6137469406662</v>
       </c>
       <c r="O22" t="n">
-        <v>15.4273858178745</v>
+        <v>15.44712746567032</v>
       </c>
       <c r="P22" t="n">
-        <v>393.2898582580603</v>
+        <v>393.5750469372614</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34947,28 +35243,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1233626945273977</v>
+        <v>-0.1397840638283908</v>
       </c>
       <c r="J23" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K23" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005288407878173085</v>
+        <v>0.006882724640075555</v>
       </c>
       <c r="M23" t="n">
-        <v>10.78225973088403</v>
+        <v>10.76178455391412</v>
       </c>
       <c r="N23" t="n">
-        <v>185.5736039622199</v>
+        <v>184.7876650537899</v>
       </c>
       <c r="O23" t="n">
-        <v>13.6225402903504</v>
+        <v>13.59366267985895</v>
       </c>
       <c r="P23" t="n">
-        <v>393.5462284613495</v>
+        <v>393.7046391423927</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35025,28 +35321,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1941347069250758</v>
+        <v>-0.2037818379976326</v>
       </c>
       <c r="J24" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K24" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01374555589506743</v>
+        <v>0.01539756299427542</v>
       </c>
       <c r="M24" t="n">
-        <v>10.77723205940725</v>
+        <v>10.72858579893828</v>
       </c>
       <c r="N24" t="n">
-        <v>175.3110563940969</v>
+        <v>174.0433277909233</v>
       </c>
       <c r="O24" t="n">
-        <v>13.24050816223067</v>
+        <v>13.1925481917226</v>
       </c>
       <c r="P24" t="n">
-        <v>393.4742286438631</v>
+        <v>393.5672784761093</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35103,28 +35399,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08713169339452585</v>
+        <v>-0.08866481532798132</v>
       </c>
       <c r="J25" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K25" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003212995924110174</v>
+        <v>0.003393131847891029</v>
       </c>
       <c r="M25" t="n">
-        <v>10.17116189581363</v>
+        <v>10.08928438972395</v>
       </c>
       <c r="N25" t="n">
-        <v>152.6935789454358</v>
+        <v>151.3363585550569</v>
       </c>
       <c r="O25" t="n">
-        <v>12.35692433194587</v>
+        <v>12.3018843497676</v>
       </c>
       <c r="P25" t="n">
-        <v>391.9677780178838</v>
+        <v>391.9825494875051</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35181,28 +35477,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0952254782027904</v>
+        <v>-0.0932187514723324</v>
       </c>
       <c r="J26" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K26" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003816701774025821</v>
+        <v>0.003730981165335767</v>
       </c>
       <c r="M26" t="n">
-        <v>10.19743117129235</v>
+        <v>10.11259445445961</v>
       </c>
       <c r="N26" t="n">
-        <v>153.4382465503614</v>
+        <v>152.0819400819019</v>
       </c>
       <c r="O26" t="n">
-        <v>12.38701927625695</v>
+        <v>12.33215066733706</v>
       </c>
       <c r="P26" t="n">
-        <v>395.0370140561439</v>
+        <v>395.0176350935091</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35259,28 +35555,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2178543545467931</v>
+        <v>0.2204211580756814</v>
       </c>
       <c r="J27" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K27" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01960666723574334</v>
+        <v>0.02045390321392637</v>
       </c>
       <c r="M27" t="n">
-        <v>10.08742411685163</v>
+        <v>10.00655586195022</v>
       </c>
       <c r="N27" t="n">
-        <v>154.151021854631</v>
+        <v>152.7712312865648</v>
       </c>
       <c r="O27" t="n">
-        <v>12.41575699885557</v>
+        <v>12.36006599038067</v>
       </c>
       <c r="P27" t="n">
-        <v>392.7191527737737</v>
+        <v>392.6943037969477</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35337,28 +35633,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4587389219400315</v>
+        <v>0.4694011147148854</v>
       </c>
       <c r="J28" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K28" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L28" t="n">
-        <v>0.07771923386575941</v>
+        <v>0.08238452381966754</v>
       </c>
       <c r="M28" t="n">
-        <v>10.17235736926013</v>
+        <v>10.12502640186228</v>
       </c>
       <c r="N28" t="n">
-        <v>162.5256219842828</v>
+        <v>161.4329743944244</v>
       </c>
       <c r="O28" t="n">
-        <v>12.74855372127689</v>
+        <v>12.7056276662912</v>
       </c>
       <c r="P28" t="n">
-        <v>390.6403203955313</v>
+        <v>390.5370772662834</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35415,28 +35711,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7069791000125895</v>
+        <v>0.7220783059476563</v>
       </c>
       <c r="J29" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K29" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1584001611310364</v>
+        <v>0.1662121186204053</v>
       </c>
       <c r="M29" t="n">
-        <v>10.69390435885994</v>
+        <v>10.66542490336264</v>
       </c>
       <c r="N29" t="n">
-        <v>173.5932889995836</v>
+        <v>172.7968491011763</v>
       </c>
       <c r="O29" t="n">
-        <v>13.17548059842917</v>
+        <v>13.14522153108027</v>
       </c>
       <c r="P29" t="n">
-        <v>380.7418615333696</v>
+        <v>380.5959565972991</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35493,28 +35789,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7423511125138686</v>
+        <v>0.7619807730311593</v>
       </c>
       <c r="J30" t="n">
+        <v>223</v>
+      </c>
+      <c r="K30" t="n">
         <v>221</v>
       </c>
-      <c r="K30" t="n">
-        <v>219</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.1620834727964735</v>
+        <v>0.1709927086162005</v>
       </c>
       <c r="M30" t="n">
-        <v>10.99955838323136</v>
+        <v>10.98873671703844</v>
       </c>
       <c r="N30" t="n">
-        <v>184.4083945055643</v>
+        <v>184.1938847308022</v>
       </c>
       <c r="O30" t="n">
-        <v>13.5797052436923</v>
+        <v>13.57180477058236</v>
       </c>
       <c r="P30" t="n">
-        <v>372.3936901358913</v>
+        <v>372.2036054923498</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35571,28 +35867,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.684762461053996</v>
+        <v>0.70103878633544</v>
       </c>
       <c r="J31" t="n">
+        <v>223</v>
+      </c>
+      <c r="K31" t="n">
         <v>221</v>
       </c>
-      <c r="K31" t="n">
-        <v>219</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.1198703643981371</v>
+        <v>0.1264335395403119</v>
       </c>
       <c r="M31" t="n">
-        <v>12.05766413997289</v>
+        <v>12.03363628791661</v>
       </c>
       <c r="N31" t="n">
-        <v>221.0428320622218</v>
+        <v>220.3920619695269</v>
       </c>
       <c r="O31" t="n">
-        <v>14.86750927567297</v>
+        <v>14.84560749748985</v>
       </c>
       <c r="P31" t="n">
-        <v>367.7808179262174</v>
+        <v>367.6222049078847</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35649,28 +35945,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5655471360850365</v>
+        <v>0.576167872961488</v>
       </c>
       <c r="J32" t="n">
+        <v>223</v>
+      </c>
+      <c r="K32" t="n">
         <v>221</v>
       </c>
-      <c r="K32" t="n">
-        <v>219</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.07132212805926375</v>
+        <v>0.07504540898350853</v>
       </c>
       <c r="M32" t="n">
-        <v>12.46173412065805</v>
+        <v>12.39598504357559</v>
       </c>
       <c r="N32" t="n">
-        <v>267.3869136743419</v>
+        <v>265.5660535391626</v>
       </c>
       <c r="O32" t="n">
-        <v>16.3519697184878</v>
+        <v>16.29619751780036</v>
       </c>
       <c r="P32" t="n">
-        <v>367.0542329876667</v>
+        <v>366.9507405330369</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35727,28 +36023,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4592711619651458</v>
+        <v>0.4623066501270794</v>
       </c>
       <c r="J33" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K33" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L33" t="n">
-        <v>0.07363475330847813</v>
+        <v>0.07588394301612655</v>
       </c>
       <c r="M33" t="n">
-        <v>10.30719129177275</v>
+        <v>10.24220264904562</v>
       </c>
       <c r="N33" t="n">
-        <v>170.7097745187442</v>
+        <v>169.2622556708617</v>
       </c>
       <c r="O33" t="n">
-        <v>13.06559506944648</v>
+        <v>13.01008284642576</v>
       </c>
       <c r="P33" t="n">
-        <v>368.958662009851</v>
+        <v>368.9290684619177</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35805,28 +36101,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4409549519305561</v>
+        <v>0.4426563516844631</v>
       </c>
       <c r="J34" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K34" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L34" t="n">
-        <v>0.04698060375058233</v>
+        <v>0.04820986053881648</v>
       </c>
       <c r="M34" t="n">
-        <v>12.55260680651269</v>
+        <v>12.47247249917949</v>
       </c>
       <c r="N34" t="n">
-        <v>255.3611475153683</v>
+        <v>253.1838050790959</v>
       </c>
       <c r="O34" t="n">
-        <v>15.98002338907451</v>
+        <v>15.91175053471792</v>
       </c>
       <c r="P34" t="n">
-        <v>364.3886247614651</v>
+        <v>364.3722297987666</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -35883,28 +36179,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1148800658841188</v>
+        <v>0.1176051871512841</v>
       </c>
       <c r="J35" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K35" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003062690052340167</v>
+        <v>0.00327095501841046</v>
       </c>
       <c r="M35" t="n">
-        <v>13.0657759034801</v>
+        <v>12.99136560549116</v>
       </c>
       <c r="N35" t="n">
-        <v>278.1233043796506</v>
+        <v>275.8371092110127</v>
       </c>
       <c r="O35" t="n">
-        <v>16.67702924323306</v>
+        <v>16.60834456563967</v>
       </c>
       <c r="P35" t="n">
-        <v>370.0114511478253</v>
+        <v>369.9851595661987</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -35961,28 +36257,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3348370625022432</v>
+        <v>0.3395984827840481</v>
       </c>
       <c r="J36" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K36" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L36" t="n">
-        <v>0.02376086238945707</v>
+        <v>0.02488860880263899</v>
       </c>
       <c r="M36" t="n">
-        <v>13.0855035685957</v>
+        <v>13.00342783439019</v>
       </c>
       <c r="N36" t="n">
-        <v>296.8714765843846</v>
+        <v>294.3922790851445</v>
       </c>
       <c r="O36" t="n">
-        <v>17.22995869363547</v>
+        <v>17.157863476702</v>
       </c>
       <c r="P36" t="n">
-        <v>368.6860972489689</v>
+        <v>368.639961151706</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -36039,28 +36335,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3872367814758471</v>
+        <v>0.3857777240606099</v>
       </c>
       <c r="J37" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K37" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L37" t="n">
-        <v>0.04185968995583056</v>
+        <v>0.04235469496591426</v>
       </c>
       <c r="M37" t="n">
-        <v>11.27484382485764</v>
+        <v>11.19377196387509</v>
       </c>
       <c r="N37" t="n">
-        <v>224.5903377810013</v>
+        <v>222.595893034735</v>
       </c>
       <c r="O37" t="n">
-        <v>14.98633837136348</v>
+        <v>14.91964788574901</v>
       </c>
       <c r="P37" t="n">
-        <v>375.8849667363751</v>
+        <v>375.8990500623768</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -36117,28 +36413,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1596329058260894</v>
+        <v>0.1777050005925202</v>
       </c>
       <c r="J38" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K38" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L38" t="n">
-        <v>0.004647298070744155</v>
+        <v>0.005846093180111311</v>
       </c>
       <c r="M38" t="n">
-        <v>14.16487445786477</v>
+        <v>14.13889377356274</v>
       </c>
       <c r="N38" t="n">
-        <v>353.0752193343043</v>
+        <v>351.1804729414462</v>
       </c>
       <c r="O38" t="n">
-        <v>18.79029588203188</v>
+        <v>18.73980984272376</v>
       </c>
       <c r="P38" t="n">
-        <v>376.1199736973838</v>
+        <v>375.9445559553338</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -36195,28 +36491,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1771461006943458</v>
+        <v>0.2007188914368439</v>
       </c>
       <c r="J39" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K39" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L39" t="n">
-        <v>0.008161347176887435</v>
+        <v>0.01057965584598242</v>
       </c>
       <c r="M39" t="n">
-        <v>12.3081312851113</v>
+        <v>12.33748750045812</v>
       </c>
       <c r="N39" t="n">
-        <v>247.2122126358165</v>
+        <v>246.8998922369056</v>
       </c>
       <c r="O39" t="n">
-        <v>15.72298357932795</v>
+        <v>15.71304847051983</v>
       </c>
       <c r="P39" t="n">
-        <v>388.3067266105467</v>
+        <v>388.077977280671</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -36273,28 +36569,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1426162585871124</v>
+        <v>0.1628366087160391</v>
       </c>
       <c r="J40" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K40" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L40" t="n">
-        <v>0.005190015715272001</v>
+        <v>0.006850897414441115</v>
       </c>
       <c r="M40" t="n">
-        <v>12.30441972248095</v>
+        <v>12.29852007801201</v>
       </c>
       <c r="N40" t="n">
-        <v>254.3378137442616</v>
+        <v>253.4624906446048</v>
       </c>
       <c r="O40" t="n">
-        <v>15.94797208877234</v>
+        <v>15.92050535142037</v>
       </c>
       <c r="P40" t="n">
-        <v>398.1349142379963</v>
+        <v>397.9390060727109</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -36351,28 +36647,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2464481066166298</v>
+        <v>0.2665821646299506</v>
       </c>
       <c r="J41" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K41" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L41" t="n">
-        <v>0.01425316711909319</v>
+        <v>0.01687590673239958</v>
       </c>
       <c r="M41" t="n">
-        <v>13.10300458423951</v>
+        <v>13.07492540869457</v>
       </c>
       <c r="N41" t="n">
-        <v>274.0352168499104</v>
+        <v>272.9895439616841</v>
       </c>
       <c r="O41" t="n">
-        <v>16.55400908692243</v>
+        <v>16.52239522471497</v>
       </c>
       <c r="P41" t="n">
-        <v>401.8775866893156</v>
+        <v>401.6825229210456</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -36429,28 +36725,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4304181021034942</v>
+        <v>0.4517065983584452</v>
       </c>
       <c r="J42" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K42" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L42" t="n">
-        <v>0.03908950779031184</v>
+        <v>0.04349524404639948</v>
       </c>
       <c r="M42" t="n">
-        <v>13.43973502574804</v>
+        <v>13.41832104315433</v>
       </c>
       <c r="N42" t="n">
-        <v>292.2863413804392</v>
+        <v>291.1125988697769</v>
       </c>
       <c r="O42" t="n">
-        <v>17.09638386853896</v>
+        <v>17.06202212135997</v>
       </c>
       <c r="P42" t="n">
-        <v>403.9516185208744</v>
+        <v>403.7422851892472</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -36507,28 +36803,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5097571856228673</v>
+        <v>0.5162083679990508</v>
       </c>
       <c r="J43" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K43" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L43" t="n">
-        <v>0.05425960792641737</v>
+        <v>0.05656644896057406</v>
       </c>
       <c r="M43" t="n">
-        <v>13.41281212229227</v>
+        <v>13.32949235427257</v>
       </c>
       <c r="N43" t="n">
-        <v>297.0513566660785</v>
+        <v>294.6070188439144</v>
       </c>
       <c r="O43" t="n">
-        <v>17.23517788321544</v>
+        <v>17.16412010106881</v>
       </c>
       <c r="P43" t="n">
-        <v>405.6520933441449</v>
+        <v>405.5898980296128</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -36566,7 +36862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR222"/>
+  <dimension ref="A1:AR224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85257,6 +85553,450 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>-34.468061260796475,172.6643590604828</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>-34.46766354416473,172.66516023077963</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>-34.467155068683915,172.66581633219366</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-34.46664726166317,172.666473314032</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-34.466119618783644,172.6671006251714</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-34.465565019218715,172.66768322272006</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-34.464729596518374,172.66793818527992</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-34.46444427513786,172.66885716889107</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-34.46422959182468,172.6698602353715</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-34.463433698533215,172.67017153468692</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-34.462656427520564,172.67050500427868</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-34.46189145424355,172.67076694701566</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-34.4613213287785,172.67101589917948</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-34.46072515043268,172.67136523243758</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-34.46006727276573,172.67179907538366</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>-34.459401839372276,172.67220784763796</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>-34.45873153121351,172.67260045165781</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>-34.45805295893983,172.67296563252552</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>-34.457371576643155,172.6733215014213</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>-34.456699278150595,172.67370755368776</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>-34.4560215505111,172.6740755967622</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>-34.455310631796365,172.67433344293084</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>-34.454609259244734,172.67462300801537</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>-34.45389413867746,172.67486694044717</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>-34.45318261748816,172.6751228447029</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>-34.45246320275402,172.6753525572753</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>-34.45175557110109,172.67554010869821</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>-34.45106809921635,172.67573707229187</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>-34.45035367745593,172.67592780383393</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>-34.44963596711391,172.67615766511773</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>-34.44892534652199,172.6764314396479</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>-34.44821086910163,172.6766813857217</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>-34.44749258676138,172.67690782445638</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>-34.446767875273906,172.67709451604307</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>-34.44603252204796,172.67721539160726</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>-34.44529878548744,172.6773463112416</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>-34.44455627196235,172.6774229558692</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>-34.44380344489526,172.67743581808207</t>
+        </is>
+      </c>
+      <c r="AN223" t="inlineStr">
+        <is>
+          <t>-34.44307728049809,172.6775320451723</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>-34.44235078295103,172.67757855293996</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>-34.441610603882836,172.67761539168768</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>-34.440880480195275,172.67777370295036</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>-34.46806505042837,172.66436402419413</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>-34.467666355809705,172.66516391353565</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>-34.467153662867915,172.66581449081937</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-34.46664145505869,172.6664657083708</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-34.46611377372107,172.6670930626226</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-34.46555669184627,172.6676729523359</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-34.46470564151343,172.66790967393825</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-34.46442365984234,172.66883263223093</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-34.4641849577897,172.66980711056</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-34.46342721215453,172.67016381445305</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-34.462656427520564,172.67050500427868</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-34.46187534059017,172.67074361708504</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-34.46130861667672,172.67098571627815</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-34.46071042119815,172.6713163219107</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-34.460049462256414,172.6717399329231</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>-34.45938495342245,172.67215177523644</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>-34.45872441328913,172.67257681545973</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>-34.45804621082501,172.67294322434142</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>-34.45737330217622,172.67332723132728</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>-34.4566987235191,172.67370571194516</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>-34.45601862330965,172.67406587652331</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>-34.45531180267196,172.67433733099588</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>-34.45460688669237,172.6746151296286</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>-34.453889763336946,172.67485241159073</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>-34.45317728698889,172.67510514419416</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>-34.45246357249832,172.67535378504635</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>-34.45176281961652,172.67556908054112</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>-34.451076322120436,172.67578248495255</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>-34.4503697866551,172.6760274939996</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>-34.449661365175494,172.67631483880197</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>-34.4489428366561,172.6765396759826</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>-34.44822197083728,172.67675008798474</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>-34.447505812040035,172.67698966816164</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>-34.44678476069272,172.6771990101387</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>-34.446045160182194,172.67729360123315</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>-34.44530750439192,172.67740026686994</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>-34.44457498734573,172.67753877248984</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>-34.4438182238752,172.67752727391718</t>
+        </is>
+      </c>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t>-34.44308943453093,172.67761976011687</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>-34.442361308105056,172.67767316752705</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>-34.441619674957806,172.67770035532064</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>-34.44089095735704,172.67787183673022</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
